--- a/test_data/PD_2025_Mar_Apr.xlsx
+++ b/test_data/PD_2025_Mar_Apr.xlsx
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>281616.82</v>
+        <v>281615</v>
       </c>
     </row>
     <row r="6">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>797115.49</v>
+        <v>803975.33</v>
       </c>
     </row>
     <row r="8">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1171487.66</v>
+        <v>1172114.58</v>
       </c>
     </row>
     <row r="10">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>795526.28</v>
+        <v>790284.34</v>
       </c>
     </row>
     <row r="12">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>408202.16</v>
+        <v>410406.66</v>
       </c>
     </row>
     <row r="14">
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>637926</v>
+        <v>640658.75</v>
       </c>
     </row>
     <row r="16">
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1047874.61</v>
+        <v>1040964.23</v>
       </c>
     </row>
     <row r="18">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>293054.1</v>
+        <v>293881.1</v>
       </c>
     </row>
     <row r="20">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>948372.9</v>
+        <v>950170.84</v>
       </c>
     </row>
     <row r="22">
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>778887.54</v>
+        <v>778130.77</v>
       </c>
     </row>
     <row r="24">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>247573.46</v>
+        <v>247725.77</v>
       </c>
     </row>
     <row r="26">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>911066.76</v>
+        <v>911157.97</v>
       </c>
     </row>
     <row r="28">
@@ -1104,7 +1104,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>410681.93</v>
+        <v>410251.9</v>
       </c>
     </row>
     <row r="30">
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>761108.4</v>
+        <v>760728.9</v>
       </c>
     </row>
     <row r="32">
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>603706.1800000001</v>
+        <v>606153.58</v>
       </c>
     </row>
     <row r="34">
@@ -1242,7 +1242,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>318283.74</v>
+        <v>320488.94</v>
       </c>
     </row>
     <row r="36">
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1042063.89</v>
+        <v>1037638.19</v>
       </c>
     </row>
     <row r="38">
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>180495.19</v>
+        <v>180383.23</v>
       </c>
     </row>
     <row r="40">
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>759771.15</v>
+        <v>759026.55</v>
       </c>
     </row>
     <row r="42">
@@ -1426,7 +1426,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>856197.09</v>
+        <v>858853.5</v>
       </c>
     </row>
     <row r="44">
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1115865.42</v>
+        <v>1115390.14</v>
       </c>
     </row>
     <row r="46">
@@ -1518,7 +1518,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1178456.6</v>
+        <v>1179512.2</v>
       </c>
     </row>
     <row r="48">
@@ -1564,7 +1564,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>481184.93</v>
+        <v>482089.42</v>
       </c>
     </row>
     <row r="50">
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>333231.9</v>
+        <v>336171.48</v>
       </c>
     </row>
     <row r="52">
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>455651.28</v>
+        <v>455827.05</v>
       </c>
     </row>
     <row r="54">
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1084024.43</v>
+        <v>1094189.81</v>
       </c>
     </row>
     <row r="56">
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1113777.21</v>
+        <v>1119890.96</v>
       </c>
     </row>
     <row r="58">
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1051437.09</v>
+        <v>1045203.97</v>
       </c>
     </row>
     <row r="60">
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>971786.37</v>
+        <v>975193.53</v>
       </c>
     </row>
     <row r="63">
@@ -1909,7 +1909,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1603051.03</v>
+        <v>1595272.07</v>
       </c>
     </row>
     <row r="65">
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1864055.29</v>
+        <v>1872883.05</v>
       </c>
     </row>
     <row r="67">
@@ -2001,7 +2001,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1082128.51</v>
+        <v>1076128.19</v>
       </c>
     </row>
     <row r="69">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1945639.44</v>
+        <v>1953878</v>
       </c>
     </row>
     <row r="71">
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1797307.57</v>
+        <v>1797699</v>
       </c>
     </row>
     <row r="73">
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2065098.29</v>
+        <v>2073992.67</v>
       </c>
     </row>
     <row r="75">
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1227264.93</v>
+        <v>1226353.38</v>
       </c>
     </row>
     <row r="77">
@@ -2231,7 +2231,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1557381.83</v>
+        <v>1555967.39</v>
       </c>
     </row>
     <row r="79">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2243145.05</v>
+        <v>2239112.5</v>
       </c>
     </row>
     <row r="81">
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1691469.78</v>
+        <v>1690365.84</v>
       </c>
     </row>
     <row r="83">
@@ -2369,7 +2369,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1242329.76</v>
+        <v>1235829.12</v>
       </c>
     </row>
     <row r="85">
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>406927.53</v>
+        <v>407343.58</v>
       </c>
     </row>
     <row r="87">
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1399648.25</v>
+        <v>1405658.49</v>
       </c>
     </row>
     <row r="89">
@@ -2507,7 +2507,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>567476.48</v>
+        <v>571324.13</v>
       </c>
     </row>
     <row r="91">
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>918344.76</v>
+        <v>921320.49</v>
       </c>
     </row>
     <row r="93">
@@ -2599,7 +2599,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1688318.59</v>
+        <v>1677064.48</v>
       </c>
     </row>
     <row r="95">
@@ -2645,7 +2645,7 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2404685.88</v>
+        <v>2400489.72</v>
       </c>
     </row>
     <row r="97">
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2155486.99</v>
+        <v>2149046.01</v>
       </c>
     </row>
     <row r="99">
@@ -2760,7 +2760,7 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4749354.74</v>
+        <v>4739893.73</v>
       </c>
     </row>
     <row r="102">
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>3638553.03</v>
+        <v>3664218.21</v>
       </c>
     </row>
     <row r="104">
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>3937173.43</v>
+        <v>3949435.56</v>
       </c>
     </row>
     <row r="106">
@@ -2898,7 +2898,7 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>3272087.03</v>
+        <v>3266262.29</v>
       </c>
     </row>
     <row r="108">
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2009883.35</v>
+        <v>2012567.98</v>
       </c>
     </row>
     <row r="110">
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>2805680.94</v>
+        <v>2789369.92</v>
       </c>
     </row>
     <row r="112">
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1929987.25</v>
+        <v>1935017.53</v>
       </c>
     </row>
     <row r="114">
@@ -3082,7 +3082,7 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>4048081.42</v>
+        <v>4051658.05</v>
       </c>
     </row>
     <row r="116">
@@ -3128,7 +3128,7 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>4906951.99</v>
+        <v>4921100.63</v>
       </c>
     </row>
   </sheetData>
